--- a/datasets/tenant-inputs/generated/harbortrust-bank/standard-2026-07-v3/core-dimensions/06_infrastructure_platforms.xlsx
+++ b/datasets/tenant-inputs/generated/harbortrust-bank/standard-2026-07-v3/core-dimensions/06_infrastructure_platforms.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="Re0f3b919d7244a73"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client Intake" sheetId="2" r:id="R4cba4f855134425b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questionnaire" sheetId="3" r:id="R13a51f1713624907"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Examples" sheetId="4" r:id="R2ba2825458ab4db4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference Values" sheetId="5" r:id="R715d6f05d5cb4e0c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationship Expectations" sheetId="6" r:id="Rf1a8f73f7f524764"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CMDB Mapping" sheetId="7" r:id="R9100ba2986aa4b70"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="R834335de9f8a4c66"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client Intake" sheetId="2" r:id="Rc6847c1f1e8548fe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questionnaire" sheetId="3" r:id="R4f40bad3319f40b8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Examples" sheetId="4" r:id="R1980be6bdd4e47d5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference Values" sheetId="5" r:id="Ra81a7f7c97b24dd1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationship Expectations" sheetId="6" r:id="R431b71763b4145bf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CMDB Mapping" sheetId="7" r:id="Rb2f347d4731a47ee"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -642,7 +642,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6c25e84b352948d0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R511d70ac978c4b16"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -833,7 +833,7 @@
         <x:v>Infrastructure operations / platform support</x:v>
       </x:c>
       <x:c r="P6" s="78" t="str">
-        <x:v>Need asset IDs, relationship links, DR evidence, patch/version posture.</x:v>
+        <x:v>Validate Executive Office Primary Northeast Data Center Hosting Segment (record 1) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for infrastructure platforms.</x:v>
       </x:c>
       <x:c r="Q6" s="41" t="str">
         <x:v>Medium</x:v>
@@ -886,7 +886,7 @@
         <x:v>Cloud platform team</x:v>
       </x:c>
       <x:c r="P7" s="79" t="str">
-        <x:v>Network, security, cost allocation, and data access controls need validation before active use.</x:v>
+        <x:v>Confirm Executive Office Azure and AWS hybrid cloud Target Landing Zone (record 2) current-vs-target status, module boundary, volume baseline, and relationship links before this infrastructure platforms record is used downstream.</x:v>
       </x:c>
       <x:c r="Q7" s="45" t="str">
         <x:v>Medium</x:v>
@@ -939,7 +939,7 @@
         <x:v>Infrastructure operations / platform support</x:v>
       </x:c>
       <x:c r="P8" t="str">
-        <x:v>Need asset IDs, relationship links, DR evidence, patch/version posture.</x:v>
+        <x:v>Attach client evidence for Retail Deposits and Branch Operations Primary Northeast Data Center Hosting Segment (record 3), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="Q8" t="str">
         <x:v>High</x:v>
@@ -992,7 +992,7 @@
         <x:v>Cloud platform team</x:v>
       </x:c>
       <x:c r="P9" t="str">
-        <x:v>Network, security, cost allocation, and data access controls need validation before active use.</x:v>
+        <x:v>Reconcile Retail Deposits and Branch Operations Azure and AWS hybrid cloud Target Landing Zone (record 4) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="Q9" t="str">
         <x:v>Medium</x:v>
@@ -1045,7 +1045,7 @@
         <x:v>Infrastructure operations / platform support</x:v>
       </x:c>
       <x:c r="P10" t="str">
-        <x:v>Need asset IDs, relationship links, DR evidence, patch/version posture.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Commercial Lending and Treasury Primary Northeast Data Center Hosting Segment (record 5) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="Q10" t="str">
         <x:v>High</x:v>
@@ -1098,7 +1098,7 @@
         <x:v>Cloud platform team</x:v>
       </x:c>
       <x:c r="P11" t="str">
-        <x:v>Network, security, cost allocation, and data access controls need validation before active use.</x:v>
+        <x:v>Validate Commercial Lending and Treasury Azure and AWS hybrid cloud Target Landing Zone (record 6) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for infrastructure platforms.</x:v>
       </x:c>
       <x:c r="Q11" t="str">
         <x:v>Medium</x:v>
@@ -1151,7 +1151,7 @@
         <x:v>Infrastructure operations / platform support</x:v>
       </x:c>
       <x:c r="P12" t="str">
-        <x:v>Need asset IDs, relationship links, DR evidence, patch/version posture.</x:v>
+        <x:v>Confirm Cards Operations Primary Northeast Data Center Hosting Segment (record 7) current-vs-target status, module boundary, volume baseline, and relationship links before this infrastructure platforms record is used downstream.</x:v>
       </x:c>
       <x:c r="Q12" t="str">
         <x:v>High</x:v>
@@ -1204,7 +1204,7 @@
         <x:v>Cloud platform team</x:v>
       </x:c>
       <x:c r="P13" t="str">
-        <x:v>Network, security, cost allocation, and data access controls need validation before active use.</x:v>
+        <x:v>Attach client evidence for Cards Operations Azure and AWS hybrid cloud Target Landing Zone (record 8), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="Q13" t="str">
         <x:v>Medium</x:v>
@@ -1257,7 +1257,7 @@
         <x:v>Infrastructure operations / platform support</x:v>
       </x:c>
       <x:c r="P14" t="str">
-        <x:v>Need asset IDs, relationship links, DR evidence, patch/version posture.</x:v>
+        <x:v>Reconcile Payments Operations Primary Northeast Data Center Hosting Segment (record 9) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="Q14" t="str">
         <x:v>High</x:v>
@@ -1310,7 +1310,7 @@
         <x:v>Cloud platform team</x:v>
       </x:c>
       <x:c r="P15" t="str">
-        <x:v>Network, security, cost allocation, and data access controls need validation before active use.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Payments Operations Azure and AWS hybrid cloud Target Landing Zone (record 10) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="Q15" t="str">
         <x:v>Medium</x:v>
@@ -1363,7 +1363,7 @@
         <x:v>Infrastructure operations / platform support</x:v>
       </x:c>
       <x:c r="P16" t="str">
-        <x:v>Need asset IDs, relationship links, DR evidence, patch/version posture.</x:v>
+        <x:v>Validate Consumer Lending Operations Primary Northeast Data Center Hosting Segment (record 11) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for infrastructure platforms.</x:v>
       </x:c>
       <x:c r="Q16" t="str">
         <x:v>Medium</x:v>
@@ -1416,7 +1416,7 @@
         <x:v>Cloud platform team</x:v>
       </x:c>
       <x:c r="P17" t="str">
-        <x:v>Network, security, cost allocation, and data access controls need validation before active use.</x:v>
+        <x:v>Confirm Consumer Lending Operations Azure and AWS hybrid cloud Target Landing Zone (record 12) current-vs-target status, module boundary, volume baseline, and relationship links before this infrastructure platforms record is used downstream.</x:v>
       </x:c>
       <x:c r="Q17" t="str">
         <x:v>Medium</x:v>
@@ -1469,7 +1469,7 @@
         <x:v>Infrastructure operations / platform support</x:v>
       </x:c>
       <x:c r="P18" t="str">
-        <x:v>Need asset IDs, relationship links, DR evidence, patch/version posture.</x:v>
+        <x:v>Attach client evidence for Wealth Advisory and Brokerage Primary Northeast Data Center Hosting Segment (record 13), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="Q18" t="str">
         <x:v>High</x:v>
@@ -1522,7 +1522,7 @@
         <x:v>Cloud platform team</x:v>
       </x:c>
       <x:c r="P19" t="str">
-        <x:v>Network, security, cost allocation, and data access controls need validation before active use.</x:v>
+        <x:v>Reconcile Wealth Advisory and Brokerage Azure and AWS hybrid cloud Target Landing Zone (record 14) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="Q19" t="str">
         <x:v>Medium</x:v>
@@ -1575,7 +1575,7 @@
         <x:v>Infrastructure operations / platform support</x:v>
       </x:c>
       <x:c r="P20" t="str">
-        <x:v>Need asset IDs, relationship links, DR evidence, patch/version posture.</x:v>
+        <x:v>Validate Fraud and Risk Operations Primary Northeast Data Center Hosting Segment (record 15) against Fraud Analyst Copilot evidence: queue aging mixed with model quality signals; confirm model-risk-approved evaluation set owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="Q20" t="str">
         <x:v>High</x:v>
@@ -1628,7 +1628,7 @@
         <x:v>Cloud platform team</x:v>
       </x:c>
       <x:c r="P21" t="str">
-        <x:v>Network, security, cost allocation, and data access controls need validation before active use.</x:v>
+        <x:v>Validate Fraud and Risk Operations Azure and AWS hybrid cloud Target Landing Zone (record 16) against Fraud Analyst Copilot evidence: case outcome feedback gaps; confirm fraud analyst copilot with cited case packet owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="Q21" t="str">
         <x:v>Medium</x:v>
@@ -1681,7 +1681,7 @@
         <x:v>Infrastructure operations / platform support</x:v>
       </x:c>
       <x:c r="P22" t="str">
-        <x:v>Need asset IDs, relationship links, DR evidence, patch/version posture.</x:v>
+        <x:v>Confirm Compliance and Model Risk Management Primary Northeast Data Center Hosting Segment (record 17) current-vs-target status, module boundary, volume baseline, and relationship links before this infrastructure platforms record is used downstream.</x:v>
       </x:c>
       <x:c r="Q22" t="str">
         <x:v>High</x:v>
@@ -1734,7 +1734,7 @@
         <x:v>Cloud platform team</x:v>
       </x:c>
       <x:c r="P23" t="str">
-        <x:v>Network, security, cost allocation, and data access controls need validation before active use.</x:v>
+        <x:v>Attach client evidence for Compliance and Model Risk Management Azure and AWS hybrid cloud Target Landing Zone (record 18), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="Q23" t="str">
         <x:v>Medium</x:v>
@@ -1787,7 +1787,7 @@
         <x:v>Infrastructure operations / platform support</x:v>
       </x:c>
       <x:c r="P24" t="str">
-        <x:v>Need asset IDs, relationship links, DR evidence, patch/version posture.</x:v>
+        <x:v>Reconcile Contact Center and Servicing Primary Northeast Data Center Hosting Segment (record 19) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="Q24" t="str">
         <x:v>High</x:v>
@@ -1840,7 +1840,7 @@
         <x:v>Cloud platform team</x:v>
       </x:c>
       <x:c r="P25" t="str">
-        <x:v>Network, security, cost allocation, and data access controls need validation before active use.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Contact Center and Servicing Azure and AWS hybrid cloud Target Landing Zone (record 20) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="Q25" t="str">
         <x:v>Medium</x:v>
@@ -1893,7 +1893,7 @@
         <x:v>Infrastructure operations / platform support</x:v>
       </x:c>
       <x:c r="P26" t="str">
-        <x:v>Need asset IDs, relationship links, DR evidence, patch/version posture.</x:v>
+        <x:v>Validate Digital Account Opening and Onboarding Primary Northeast Data Center Hosting Segment (record 21) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for infrastructure platforms.</x:v>
       </x:c>
       <x:c r="Q26" t="str">
         <x:v>Medium</x:v>
@@ -1946,7 +1946,7 @@
         <x:v>Cloud platform team</x:v>
       </x:c>
       <x:c r="P27" t="str">
-        <x:v>Network, security, cost allocation, and data access controls need validation before active use.</x:v>
+        <x:v>Confirm Digital Account Opening and Onboarding Azure and AWS hybrid cloud Target Landing Zone (record 22) current-vs-target status, module boundary, volume baseline, and relationship links before this infrastructure platforms record is used downstream.</x:v>
       </x:c>
       <x:c r="Q27" t="str">
         <x:v>Medium</x:v>
@@ -1999,7 +1999,7 @@
         <x:v>Infrastructure operations / platform support</x:v>
       </x:c>
       <x:c r="P28" t="str">
-        <x:v>Need asset IDs, relationship links, DR evidence, patch/version posture.</x:v>
+        <x:v>Attach client evidence for Core Banking Modernization Primary Northeast Data Center Hosting Segment (record 23), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="Q28" t="str">
         <x:v>High</x:v>
@@ -2052,7 +2052,7 @@
         <x:v>Cloud platform team</x:v>
       </x:c>
       <x:c r="P29" t="str">
-        <x:v>Network, security, cost allocation, and data access controls need validation before active use.</x:v>
+        <x:v>Reconcile Core Banking Modernization Azure and AWS hybrid cloud Target Landing Zone (record 24) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="Q29" t="str">
         <x:v>Medium</x:v>
@@ -2105,7 +2105,7 @@
         <x:v>Infrastructure operations / platform support</x:v>
       </x:c>
       <x:c r="P30" t="str">
-        <x:v>Need asset IDs, relationship links, DR evidence, patch/version posture.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Customer 360 Data Product Primary Northeast Data Center Hosting Segment (record 25) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="Q30" t="str">
         <x:v>High</x:v>
@@ -2158,7 +2158,7 @@
         <x:v>Cloud platform team</x:v>
       </x:c>
       <x:c r="P31" t="str">
-        <x:v>Network, security, cost allocation, and data access controls need validation before active use.</x:v>
+        <x:v>Validate Customer 360 Data Product Azure and AWS hybrid cloud Target Landing Zone (record 26) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for infrastructure platforms.</x:v>
       </x:c>
       <x:c r="Q31" t="str">
         <x:v>Medium</x:v>
@@ -2211,7 +2211,7 @@
         <x:v>Infrastructure operations / platform support</x:v>
       </x:c>
       <x:c r="P32" t="str">
-        <x:v>Need asset IDs, relationship links, DR evidence, patch/version posture.</x:v>
+        <x:v>Confirm Retail Banking Analytics Primary Northeast Data Center Hosting Segment (record 27) current-vs-target status, module boundary, volume baseline, and relationship links before this infrastructure platforms record is used downstream.</x:v>
       </x:c>
       <x:c r="Q32" t="str">
         <x:v>High</x:v>
@@ -2264,7 +2264,7 @@
         <x:v>Cloud platform team</x:v>
       </x:c>
       <x:c r="P33" t="str">
-        <x:v>Network, security, cost allocation, and data access controls need validation before active use.</x:v>
+        <x:v>Attach client evidence for Retail Banking Analytics Azure and AWS hybrid cloud Target Landing Zone (record 28), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="Q33" t="str">
         <x:v>Medium</x:v>
@@ -2317,7 +2317,7 @@
         <x:v>Infrastructure operations / platform support</x:v>
       </x:c>
       <x:c r="P34" t="str">
-        <x:v>Need asset IDs, relationship links, DR evidence, patch/version posture.</x:v>
+        <x:v>Reconcile Cards Portfolio Analytics Primary Northeast Data Center Hosting Segment (record 29) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="Q34" t="str">
         <x:v>High</x:v>
@@ -2370,7 +2370,7 @@
         <x:v>Cloud platform team</x:v>
       </x:c>
       <x:c r="P35" t="str">
-        <x:v>Network, security, cost allocation, and data access controls need validation before active use.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Cards Portfolio Analytics Azure and AWS hybrid cloud Target Landing Zone (record 30) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="Q35" t="str">
         <x:v>Medium</x:v>
@@ -2423,7 +2423,7 @@
         <x:v>Infrastructure operations / platform support</x:v>
       </x:c>
       <x:c r="P36" t="str">
-        <x:v>Need asset IDs, relationship links, DR evidence, patch/version posture.</x:v>
+        <x:v>Validate Payments and Settlement Analytics Primary Northeast Data Center Hosting Segment (record 31) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for infrastructure platforms.</x:v>
       </x:c>
       <x:c r="Q36" t="str">
         <x:v>Medium</x:v>
@@ -2476,7 +2476,7 @@
         <x:v>Cloud platform team</x:v>
       </x:c>
       <x:c r="P37" t="str">
-        <x:v>Network, security, cost allocation, and data access controls need validation before active use.</x:v>
+        <x:v>Confirm Payments and Settlement Analytics Azure and AWS hybrid cloud Target Landing Zone (record 32) current-vs-target status, module boundary, volume baseline, and relationship links before this infrastructure platforms record is used downstream.</x:v>
       </x:c>
       <x:c r="Q37" t="str">
         <x:v>Medium</x:v>
@@ -2529,7 +2529,7 @@
         <x:v>Infrastructure operations / platform support</x:v>
       </x:c>
       <x:c r="P38" t="str">
-        <x:v>Need asset IDs, relationship links, DR evidence, patch/version posture.</x:v>
+        <x:v>Validate Fraud and Risk Analytics Primary Northeast Data Center Hosting Segment (record 33) against Fraud Analyst Copilot evidence: queue aging mixed with model quality signals; confirm model-risk-approved evaluation set owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="Q38" t="str">
         <x:v>High</x:v>
@@ -2582,7 +2582,7 @@
         <x:v>Cloud platform team</x:v>
       </x:c>
       <x:c r="P39" t="str">
-        <x:v>Network, security, cost allocation, and data access controls need validation before active use.</x:v>
+        <x:v>Validate Fraud and Risk Analytics Azure and AWS hybrid cloud Target Landing Zone (record 34) against Fraud Analyst Copilot evidence: case outcome feedback gaps; confirm fraud analyst copilot with cited case packet owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="Q39" t="str">
         <x:v>Medium</x:v>
@@ -2635,7 +2635,7 @@
         <x:v>Infrastructure operations / platform support</x:v>
       </x:c>
       <x:c r="P40" t="str">
-        <x:v>Need asset IDs, relationship links, DR evidence, patch/version posture.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Cloud Data Platform Primary Northeast Data Center Hosting Segment (record 35) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="Q40" t="str">
         <x:v>High</x:v>
@@ -2688,7 +2688,7 @@
         <x:v>Cloud platform team</x:v>
       </x:c>
       <x:c r="P41" t="str">
-        <x:v>Network, security, cost allocation, and data access controls need validation before active use.</x:v>
+        <x:v>Validate Cloud Data Platform Azure and AWS hybrid cloud Target Landing Zone (record 36) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for infrastructure platforms.</x:v>
       </x:c>
       <x:c r="Q41" t="str">
         <x:v>Medium</x:v>
@@ -2741,7 +2741,7 @@
         <x:v>Infrastructure operations / platform support</x:v>
       </x:c>
       <x:c r="P42" t="str">
-        <x:v>Need asset IDs, relationship links, DR evidence, patch/version posture.</x:v>
+        <x:v>Confirm IT Budget and Tower Baseline Primary Northeast Data Center Hosting Segment (record 37) current-vs-target status, module boundary, volume baseline, and relationship links before this infrastructure platforms record is used downstream.</x:v>
       </x:c>
       <x:c r="Q42" t="str">
         <x:v>High</x:v>
@@ -2794,7 +2794,7 @@
         <x:v>Cloud platform team</x:v>
       </x:c>
       <x:c r="P43" t="str">
-        <x:v>Network, security, cost allocation, and data access controls need validation before active use.</x:v>
+        <x:v>Attach client evidence for IT Budget and Tower Baseline Azure and AWS hybrid cloud Target Landing Zone (record 38), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="Q43" t="str">
         <x:v>Medium</x:v>
@@ -2847,7 +2847,7 @@
         <x:v>Infrastructure operations / platform support</x:v>
       </x:c>
       <x:c r="P44" t="str">
-        <x:v>Need asset IDs, relationship links, DR evidence, patch/version posture.</x:v>
+        <x:v>Reconcile Vendor and Contract Optimization Primary Northeast Data Center Hosting Segment (record 39) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="Q44" t="str">
         <x:v>High</x:v>
@@ -2900,7 +2900,7 @@
         <x:v>Cloud platform team</x:v>
       </x:c>
       <x:c r="P45" t="str">
-        <x:v>Network, security, cost allocation, and data access controls need validation before active use.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Vendor and Contract Optimization Azure and AWS hybrid cloud Target Landing Zone (record 40) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="Q45" t="str">
         <x:v>Medium</x:v>
@@ -2953,7 +2953,7 @@
         <x:v>Infrastructure operations / platform support</x:v>
       </x:c>
       <x:c r="P46" t="str">
-        <x:v>Need asset IDs, relationship links, DR evidence, patch/version posture.</x:v>
+        <x:v>Validate Infrastructure and CMDB Primary Northeast Data Center Hosting Segment (record 41) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for infrastructure platforms.</x:v>
       </x:c>
       <x:c r="Q46" t="str">
         <x:v>Medium</x:v>
@@ -3006,7 +3006,7 @@
         <x:v>Cloud platform team</x:v>
       </x:c>
       <x:c r="P47" t="str">
-        <x:v>Network, security, cost allocation, and data access controls need validation before active use.</x:v>
+        <x:v>Confirm Infrastructure and CMDB Azure and AWS hybrid cloud Target Landing Zone (record 42) current-vs-target status, module boundary, volume baseline, and relationship links before this infrastructure platforms record is used downstream.</x:v>
       </x:c>
       <x:c r="Q47" t="str">
         <x:v>Medium</x:v>
@@ -3059,7 +3059,7 @@
         <x:v>Infrastructure operations / platform support</x:v>
       </x:c>
       <x:c r="P48" t="str">
-        <x:v>Need asset IDs, relationship links, DR evidence, patch/version posture.</x:v>
+        <x:v>Attach client evidence for Incident Problem Change Operations Primary Northeast Data Center Hosting Segment (record 43), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="Q48" t="str">
         <x:v>High</x:v>
@@ -3112,7 +3112,7 @@
         <x:v>Cloud platform team</x:v>
       </x:c>
       <x:c r="P49" t="str">
-        <x:v>Network, security, cost allocation, and data access controls need validation before active use.</x:v>
+        <x:v>Reconcile Incident Problem Change Operations Azure and AWS hybrid cloud Target Landing Zone (record 44) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="Q49" t="str">
         <x:v>Medium</x:v>
@@ -3139,7 +3139,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6101bc17c1404704"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf0ace17bdfb24c29"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3214,7 +3214,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra26f2d02e22948ef"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re52c6f5854f64523"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3418,7 +3418,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6fe836b8de9045f8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5268de06eb3f49e8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3496,7 +3496,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdf5e2ea9f8924a06"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc77663f90d19441a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3606,7 +3606,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8f7ab88134664074"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd0179dca0d6d44bd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3714,7 +3714,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9c7f9aca7f5b4122"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5c2cc4a276384307"/>
   </x:tableParts>
 </x:worksheet>
 </file>